--- a/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/analytics_backlog.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/analytics_backlog.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cash predictor 0</t>
+          <t>Anomaly detection 0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -501,17 +501,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Forecast model 1</t>
+          <t>Anomaly detection 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -545,17 +545,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cash predictor 3</t>
+          <t>Anomaly detection 3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Anomaly detection 5</t>
+          <t>Cash predictor 5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Churn model 6</t>
+          <t>Anomaly detection 6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -633,17 +633,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anomaly detection 7</t>
+          <t>Spend cube 7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cash predictor 8</t>
+          <t>Anomaly detection 8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Churn model 9</t>
+          <t>Cash predictor 9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Forecast model 10</t>
+          <t>Anomaly detection 10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Churn model 12</t>
+          <t>Anomaly detection 12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Forecast model 13</t>
+          <t>Anomaly detection 13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Churn model 14</t>
+          <t>Forecast model 14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cash predictor 16</t>
+          <t>Forecast model 16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -853,17 +853,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anomaly detection 17</t>
+          <t>Churn model 17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -875,17 +875,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anomaly detection 18</t>
+          <t>Cash predictor 18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cash predictor 19</t>
+          <t>Spend cube 19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Forecast model 20</t>
+          <t>Anomaly detection 20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Churn model 21</t>
+          <t>Cash predictor 21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spend cube 22</t>
+          <t>Churn model 22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Forecast model 23</t>
+          <t>Churn model 23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cash predictor 25</t>
+          <t>Spend cube 25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anomaly detection 26</t>
+          <t>Spend cube 26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Churn model 27</t>
+          <t>Spend cube 27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cash predictor 28</t>
+          <t>Spend cube 28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cash predictor 29</t>
+          <t>Spend cube 29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Backlog</t>
         </is>
       </c>
     </row>
